--- a/artfynd/A 16612-2024 artfynd.xlsx
+++ b/artfynd/A 16612-2024 artfynd.xlsx
@@ -1338,7 +1338,7 @@
         <v>117140330</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
